--- a/ListaRucs.xlsx
+++ b/ListaRucs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bpolar\Documents\GitHub\Contratos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34E6187D-5E73-4A10-B242-0778FA556DE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD28F81D-4208-4D74-AE91-055127563C70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{2FB8FF63-2A97-4BBC-A821-5241A1F63A8A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="296">
   <si>
     <t>RUC</t>
   </si>
@@ -918,6 +918,12 @@
   </si>
   <si>
     <t>20452663032</t>
+  </si>
+  <si>
+    <t>SOGU CONSTRUCTORA S.A.C.</t>
+  </si>
+  <si>
+    <t>20485988468</t>
   </si>
 </sst>
 </file>
@@ -977,8 +983,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C5BA2685-B410-4623-80E2-7FA47B029E69}" name="Tabla1" displayName="Tabla1" ref="A1:B147" totalsRowShown="0">
-  <autoFilter ref="A1:B147" xr:uid="{C5BA2685-B410-4623-80E2-7FA47B029E69}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C5BA2685-B410-4623-80E2-7FA47B029E69}" name="Tabla1" displayName="Tabla1" ref="A1:B148" totalsRowShown="0">
+  <autoFilter ref="A1:B148" xr:uid="{C5BA2685-B410-4623-80E2-7FA47B029E69}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{7C1DD435-7312-4292-B94D-21E7A762412C}" name="RUC"/>
     <tableColumn id="2" xr3:uid="{C603F77D-DCCC-4959-8B02-F5149DD2CA1B}" name="Razón Social"/>
@@ -1304,7 +1310,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02EE53A7-7176-41A5-94D2-50B9ACA98C71}">
-  <dimension ref="A1:C147"/>
+  <dimension ref="A1:C148"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.85546875" bestFit="1" customWidth="1"/>
@@ -2513,6 +2519,14 @@
         <v>291</v>
       </c>
     </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A148" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B148" t="s">
+        <v>294</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C1:C64">
     <sortCondition ref="C1:C64"/>

--- a/ListaRucs.xlsx
+++ b/ListaRucs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bpolar\Documents\GitHub\Contratos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD28F81D-4208-4D74-AE91-055127563C70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40630684-DC61-4F17-BED0-B21E3EFBEF58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{2FB8FF63-2A97-4BBC-A821-5241A1F63A8A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="298">
   <si>
     <t>RUC</t>
   </si>
@@ -924,6 +924,12 @@
   </si>
   <si>
     <t>20485988468</t>
+  </si>
+  <si>
+    <t>CONSAGA INGENIEROS CONTRATISTAS GENERALES S.R.L.</t>
+  </si>
+  <si>
+    <t>20445200019</t>
   </si>
 </sst>
 </file>
@@ -983,8 +989,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C5BA2685-B410-4623-80E2-7FA47B029E69}" name="Tabla1" displayName="Tabla1" ref="A1:B148" totalsRowShown="0">
-  <autoFilter ref="A1:B148" xr:uid="{C5BA2685-B410-4623-80E2-7FA47B029E69}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C5BA2685-B410-4623-80E2-7FA47B029E69}" name="Tabla1" displayName="Tabla1" ref="A1:B149" totalsRowShown="0">
+  <autoFilter ref="A1:B149" xr:uid="{C5BA2685-B410-4623-80E2-7FA47B029E69}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{7C1DD435-7312-4292-B94D-21E7A762412C}" name="RUC"/>
     <tableColumn id="2" xr3:uid="{C603F77D-DCCC-4959-8B02-F5149DD2CA1B}" name="Razón Social"/>
@@ -1310,7 +1316,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02EE53A7-7176-41A5-94D2-50B9ACA98C71}">
-  <dimension ref="A1:C148"/>
+  <dimension ref="A1:C149"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.85546875" bestFit="1" customWidth="1"/>
@@ -2527,6 +2533,14 @@
         <v>294</v>
       </c>
     </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A149" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B149" t="s">
+        <v>296</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C1:C64">
     <sortCondition ref="C1:C64"/>
